--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/107.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/107.xlsx
@@ -426,13 +426,13 @@
         <v>-5.005794649710242</v>
       </c>
       <c r="E2">
-        <v>-15.48256941507007</v>
+        <v>-14.69278543423633</v>
       </c>
       <c r="F2">
-        <v>-3.201074384131485</v>
+        <v>-3.759728674049083</v>
       </c>
       <c r="G2">
-        <v>-11.58626127998408</v>
+        <v>-8.702667992777554</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.767082992145528</v>
       </c>
       <c r="E3">
-        <v>-16.00062684154756</v>
+        <v>-15.2457211675209</v>
       </c>
       <c r="F3">
-        <v>-3.244113040911336</v>
+        <v>-3.689300877463069</v>
       </c>
       <c r="G3">
-        <v>-11.87391941165748</v>
+        <v>-8.112720762497192</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.48262953835835</v>
       </c>
       <c r="E4">
-        <v>-16.72152367577662</v>
+        <v>-15.19319539750593</v>
       </c>
       <c r="F4">
-        <v>-3.372306209964171</v>
+        <v>-3.266184061991526</v>
       </c>
       <c r="G4">
-        <v>-11.33134645825238</v>
+        <v>-8.016259411092637</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.053528542556132</v>
       </c>
       <c r="E5">
-        <v>-17.53279979425076</v>
+        <v>-15.26671517302046</v>
       </c>
       <c r="F5">
-        <v>-2.985689747362183</v>
+        <v>-3.785350906185074</v>
       </c>
       <c r="G5">
-        <v>-11.68219435471757</v>
+        <v>-8.098634478342497</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.50455173883503</v>
       </c>
       <c r="E6">
-        <v>-17.78730909042985</v>
+        <v>-16.77766316804971</v>
       </c>
       <c r="F6">
-        <v>-3.063772487117467</v>
+        <v>-3.54969363396706</v>
       </c>
       <c r="G6">
-        <v>-12.4538621974031</v>
+        <v>-8.622740716811041</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.840092219966904</v>
       </c>
       <c r="E7">
-        <v>-18.8303706225126</v>
+        <v>-17.86313838768829</v>
       </c>
       <c r="F7">
-        <v>-3.104435386186089</v>
+        <v>-3.436403622857991</v>
       </c>
       <c r="G7">
-        <v>-11.93877603700147</v>
+        <v>-7.859443270323655</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.074499127387901</v>
       </c>
       <c r="E8">
-        <v>-18.47642509407308</v>
+        <v>-17.1979553691756</v>
       </c>
       <c r="F8">
-        <v>-2.921439086498844</v>
+        <v>-3.23333763773572</v>
       </c>
       <c r="G8">
-        <v>-11.45856269933361</v>
+        <v>-8.027218691101181</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.226018133434236</v>
       </c>
       <c r="E9">
-        <v>-19.48544155856616</v>
+        <v>-19.40559550486292</v>
       </c>
       <c r="F9">
-        <v>-3.047644173784961</v>
+        <v>-3.619324541111581</v>
       </c>
       <c r="G9">
-        <v>-11.05617009339111</v>
+        <v>-9.411628410240537</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.308712639400847</v>
       </c>
       <c r="E10">
-        <v>-20.38055331634431</v>
+        <v>-19.69244263393078</v>
       </c>
       <c r="F10">
-        <v>-2.944723665824136</v>
+        <v>-3.093042020927985</v>
       </c>
       <c r="G10">
-        <v>-11.54782505063675</v>
+        <v>-8.691150905103903</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.327802629794599</v>
       </c>
       <c r="E11">
-        <v>-20.32253450735803</v>
+        <v>-19.58832848802043</v>
       </c>
       <c r="F11">
-        <v>-2.491131213603599</v>
+        <v>-3.323089589094241</v>
       </c>
       <c r="G11">
-        <v>-10.850690155674</v>
+        <v>-8.923668108470835</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.297153122427682</v>
       </c>
       <c r="E12">
-        <v>-21.83008161840753</v>
+        <v>-21.39828256482814</v>
       </c>
       <c r="F12">
-        <v>-2.673081285261108</v>
+        <v>-3.066544204447234</v>
       </c>
       <c r="G12">
-        <v>-10.10648941866259</v>
+        <v>-8.705945933115441</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.214265824261835</v>
       </c>
       <c r="E13">
-        <v>-22.87871770199371</v>
+        <v>-21.91611356760525</v>
       </c>
       <c r="F13">
-        <v>-2.48365685452814</v>
+        <v>-3.141640679715426</v>
       </c>
       <c r="G13">
-        <v>-10.56491544517572</v>
+        <v>-7.727118167274369</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.091826558287675</v>
       </c>
       <c r="E14">
-        <v>-23.87501821147325</v>
+        <v>-22.30771788589255</v>
       </c>
       <c r="F14">
-        <v>-2.40936886584508</v>
+        <v>-3.019183954926978</v>
       </c>
       <c r="G14">
-        <v>-9.758302592882108</v>
+        <v>-8.491196544492903</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.933221989340029</v>
       </c>
       <c r="E15">
-        <v>-23.92181546186852</v>
+        <v>-23.67380905436444</v>
       </c>
       <c r="F15">
-        <v>-1.863184818809226</v>
+        <v>-2.367572760169428</v>
       </c>
       <c r="G15">
-        <v>-10.35496976491621</v>
+        <v>-7.864739161920599</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.743293562205888</v>
       </c>
       <c r="E16">
-        <v>-24.98850657132328</v>
+        <v>-22.94337072540122</v>
       </c>
       <c r="F16">
-        <v>-1.684072733873708</v>
+        <v>-1.992928691640101</v>
       </c>
       <c r="G16">
-        <v>-9.420464739900121</v>
+        <v>-6.901090327013518</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.534154018042895</v>
       </c>
       <c r="E17">
-        <v>-25.78976570529246</v>
+        <v>-23.37863859007048</v>
       </c>
       <c r="F17">
-        <v>-1.700840546841176</v>
+        <v>-1.332664370992908</v>
       </c>
       <c r="G17">
-        <v>-9.458375973797946</v>
+        <v>-7.080530490434871</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.303212385034739</v>
       </c>
       <c r="E18">
-        <v>-27.24848228111725</v>
+        <v>-24.97467661170386</v>
       </c>
       <c r="F18">
-        <v>-1.211196716883402</v>
+        <v>-1.477342879728855</v>
       </c>
       <c r="G18">
-        <v>-9.046467825333053</v>
+        <v>-6.098316503944452</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.062456735664734</v>
       </c>
       <c r="E19">
-        <v>-27.3216624210812</v>
+        <v>-26.1934338783362</v>
       </c>
       <c r="F19">
-        <v>-1.274725869738902</v>
+        <v>-2.070061293984374</v>
       </c>
       <c r="G19">
-        <v>-8.575103942211022</v>
+        <v>-6.21196161265582</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.811563764610781</v>
       </c>
       <c r="E20">
-        <v>-28.60418060174154</v>
+        <v>-27.45105450890237</v>
       </c>
       <c r="F20">
-        <v>-0.6645819187980924</v>
+        <v>-1.169485104682836</v>
       </c>
       <c r="G20">
-        <v>-7.948958275686866</v>
+        <v>-5.180017432210456</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.550828579724782</v>
       </c>
       <c r="E21">
-        <v>-29.22459059774039</v>
+        <v>-28.22713985586291</v>
       </c>
       <c r="F21">
-        <v>-0.7902701048248613</v>
+        <v>-0.645011738906954</v>
       </c>
       <c r="G21">
-        <v>-8.83529168698875</v>
+        <v>-6.285739879419934</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.286888436819879</v>
       </c>
       <c r="E22">
-        <v>-29.55755344186537</v>
+        <v>-27.80669368662075</v>
       </c>
       <c r="F22">
-        <v>-0.5998665438217837</v>
+        <v>-1.037368787610343</v>
       </c>
       <c r="G22">
-        <v>-8.013762401485899</v>
+        <v>-5.427579036427441</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.013841408513079</v>
       </c>
       <c r="E23">
-        <v>-29.92359678861637</v>
+        <v>-29.17185198944706</v>
       </c>
       <c r="F23">
-        <v>-0.5230147580270597</v>
+        <v>-0.5362545542260041</v>
       </c>
       <c r="G23">
-        <v>-8.008230261936676</v>
+        <v>-5.757817580277755</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.740378623742919</v>
       </c>
       <c r="E24">
-        <v>-30.5809478113328</v>
+        <v>-29.05183837129578</v>
       </c>
       <c r="F24">
-        <v>-0.01774294864807036</v>
+        <v>-0.1722202153917334</v>
       </c>
       <c r="G24">
-        <v>-7.947839379135095</v>
+        <v>-4.964700392258135</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.465215177773413</v>
       </c>
       <c r="E25">
-        <v>-30.06579766516823</v>
+        <v>-29.93328093028178</v>
       </c>
       <c r="F25">
-        <v>-0.4401034646808571</v>
+        <v>-0.3333285631948064</v>
       </c>
       <c r="G25">
-        <v>-7.95649524160891</v>
+        <v>-4.717604721502591</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.187431984269316</v>
       </c>
       <c r="E26">
-        <v>-31.42647051448995</v>
+        <v>-30.79326757941943</v>
       </c>
       <c r="F26">
-        <v>-0.5258336922987863</v>
+        <v>0.212564726882665</v>
       </c>
       <c r="G26">
-        <v>-7.454274750941861</v>
+        <v>-4.90096922590904</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.911203393364568</v>
       </c>
       <c r="E27">
-        <v>-31.04808254759403</v>
+        <v>-29.68292650900472</v>
       </c>
       <c r="F27">
-        <v>-0.3810922276402259</v>
+        <v>-0.3409180653392555</v>
       </c>
       <c r="G27">
-        <v>-7.899782608175468</v>
+        <v>-5.050163088995432</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.62896166454018</v>
       </c>
       <c r="E28">
-        <v>-31.12774519809997</v>
+        <v>-31.00254874144691</v>
       </c>
       <c r="F28">
-        <v>-0.515551167727836</v>
+        <v>-0.1832938308323571</v>
       </c>
       <c r="G28">
-        <v>-7.914062484402171</v>
+        <v>-4.779803557383425</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.345539489849088</v>
       </c>
       <c r="E29">
-        <v>-30.90619866422271</v>
+        <v>-29.24580649846633</v>
       </c>
       <c r="F29">
-        <v>-0.6079547231427181</v>
+        <v>-0.001341274072640152</v>
       </c>
       <c r="G29">
-        <v>-7.675333928623211</v>
+        <v>-6.100006333047566</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.05983911490872</v>
       </c>
       <c r="E30">
-        <v>-29.89305902414565</v>
+        <v>-29.50464275155975</v>
       </c>
       <c r="F30">
-        <v>-0.5691324564431165</v>
+        <v>0.006774241372586605</v>
       </c>
       <c r="G30">
-        <v>-7.920634771185739</v>
+        <v>-4.953101274045498</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.772549432372646</v>
       </c>
       <c r="E31">
-        <v>-30.4823538752378</v>
+        <v>-29.61180003200325</v>
       </c>
       <c r="F31">
-        <v>-0.4998825983038834</v>
+        <v>-0.2672753748629766</v>
       </c>
       <c r="G31">
-        <v>-7.263632497116564</v>
+        <v>-5.626289814067413</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.493418988374772</v>
       </c>
       <c r="E32">
-        <v>-29.67874672749564</v>
+        <v>-28.47089402627378</v>
       </c>
       <c r="F32">
-        <v>-0.7242533646587547</v>
+        <v>-0.3475905647688055</v>
       </c>
       <c r="G32">
-        <v>-7.404249247046567</v>
+        <v>-4.758574053893818</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.224970720140066</v>
       </c>
       <c r="E33">
-        <v>-28.91164587296633</v>
+        <v>-26.97593607296561</v>
       </c>
       <c r="F33">
-        <v>-0.2927418739272418</v>
+        <v>-0.8005683683764647</v>
       </c>
       <c r="G33">
-        <v>-7.807659031672499</v>
+        <v>-5.637144094986057</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.980681220008481</v>
       </c>
       <c r="E34">
-        <v>-28.87847027238613</v>
+        <v>-28.27857879211603</v>
       </c>
       <c r="F34">
-        <v>-0.7172511750028905</v>
+        <v>-0.9545643536591012</v>
       </c>
       <c r="G34">
-        <v>-7.798209113581297</v>
+        <v>-5.548659393192511</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.769395006497332</v>
       </c>
       <c r="E35">
-        <v>-27.60483242925483</v>
+        <v>-26.67232906159536</v>
       </c>
       <c r="F35">
-        <v>-0.6183673013959079</v>
+        <v>-0.5724061644189802</v>
       </c>
       <c r="G35">
-        <v>-7.572618568926354</v>
+        <v>-5.845879004490132</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.595693466031894</v>
       </c>
       <c r="E36">
-        <v>-27.12720974719183</v>
+        <v>-26.64941498311654</v>
       </c>
       <c r="F36">
-        <v>-0.6216153299822847</v>
+        <v>-0.3436848124646059</v>
       </c>
       <c r="G36">
-        <v>-7.832622565296753</v>
+        <v>-5.387662976156796</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.469239969808793</v>
       </c>
       <c r="E37">
-        <v>-27.48382707529587</v>
+        <v>-27.6300832003216</v>
       </c>
       <c r="F37">
-        <v>-0.8415493605277619</v>
+        <v>-0.6269351054430632</v>
       </c>
       <c r="G37">
-        <v>-7.161084479719238</v>
+        <v>-4.747201339968782</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.387895279896693</v>
       </c>
       <c r="E38">
-        <v>-26.43876848617575</v>
+        <v>-24.5280694481194</v>
       </c>
       <c r="F38">
-        <v>-0.6590898429175316</v>
+        <v>-0.6798296775814228</v>
       </c>
       <c r="G38">
-        <v>-7.763205041985141</v>
+        <v>-4.941151065126</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.353208981674788</v>
       </c>
       <c r="E39">
-        <v>-25.88559727224278</v>
+        <v>-25.01205463616317</v>
       </c>
       <c r="F39">
-        <v>-0.5323048984494561</v>
+        <v>-0.604208017379856</v>
       </c>
       <c r="G39">
-        <v>-7.49871889696454</v>
+        <v>-6.802108997451309</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.362816473553401</v>
       </c>
       <c r="E40">
-        <v>-25.41428728294647</v>
+        <v>-24.64638036004379</v>
       </c>
       <c r="F40">
-        <v>-0.7175402752264675</v>
+        <v>-0.5240585009545869</v>
       </c>
       <c r="G40">
-        <v>-7.800309095379342</v>
+        <v>-5.725520516468141</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.407464807835061</v>
       </c>
       <c r="E41">
-        <v>-25.66343939437449</v>
+        <v>-24.94822126655105</v>
       </c>
       <c r="F41">
-        <v>-0.7809625686870061</v>
+        <v>-0.7370938877695499</v>
       </c>
       <c r="G41">
-        <v>-7.539406044301655</v>
+        <v>-5.821168124925954</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.486316062217908</v>
       </c>
       <c r="E42">
-        <v>-24.62042314703183</v>
+        <v>-24.9342011110233</v>
       </c>
       <c r="F42">
-        <v>-0.699201877663292</v>
+        <v>-0.9080564941963258</v>
       </c>
       <c r="G42">
-        <v>-8.36742230482753</v>
+        <v>-4.918746884318112</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.590736027142737</v>
       </c>
       <c r="E43">
-        <v>-23.04137143140122</v>
+        <v>-22.72102718009862</v>
       </c>
       <c r="F43">
-        <v>-0.8623140462137371</v>
+        <v>-0.5368269561013386</v>
       </c>
       <c r="G43">
-        <v>-8.055988441734392</v>
+        <v>-5.337151851470704</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.716891261722142</v>
       </c>
       <c r="E44">
-        <v>-23.31176661439921</v>
+        <v>-21.83336476206309</v>
       </c>
       <c r="F44">
-        <v>-0.7503742739712315</v>
+        <v>-0.9106418288604631</v>
       </c>
       <c r="G44">
-        <v>-8.409681157291617</v>
+        <v>-6.492955583341987</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.863623046480738</v>
       </c>
       <c r="E45">
-        <v>-22.20386639147464</v>
+        <v>-22.04831330931117</v>
       </c>
       <c r="F45">
-        <v>-1.013008987396218</v>
+        <v>-1.063695960406116</v>
       </c>
       <c r="G45">
-        <v>-8.368564169930215</v>
+        <v>-5.845783849064908</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.023169012299017</v>
       </c>
       <c r="E46">
-        <v>-21.45127023919189</v>
+        <v>-19.58825603243631</v>
       </c>
       <c r="F46">
-        <v>-0.7735205159402553</v>
+        <v>-0.3008988077426086</v>
       </c>
       <c r="G46">
-        <v>-8.283708499181415</v>
+        <v>-5.961351753610111</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.199402401429294</v>
       </c>
       <c r="E47">
-        <v>-20.79729066537418</v>
+        <v>-20.16377526559713</v>
       </c>
       <c r="F47">
-        <v>-0.8542308370972195</v>
+        <v>-0.4411993947547608</v>
       </c>
       <c r="G47">
-        <v>-7.970574963320487</v>
+        <v>-5.857067970007838</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.389633320116638</v>
       </c>
       <c r="E48">
-        <v>-20.13576665385969</v>
+        <v>-20.2118767165066</v>
       </c>
       <c r="F48">
-        <v>-0.6786293732147664</v>
+        <v>-0.4657977647808921</v>
       </c>
       <c r="G48">
-        <v>-8.190341339707416</v>
+        <v>-5.638574707585974</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.59309861467662</v>
       </c>
       <c r="E49">
-        <v>-19.9456703719657</v>
+        <v>-19.06917064235908</v>
       </c>
       <c r="F49">
-        <v>-0.7359673081017425</v>
+        <v>-0.9543067313968306</v>
       </c>
       <c r="G49">
-        <v>-8.476457297247876</v>
+        <v>-5.509918010240147</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.813610131447803</v>
       </c>
       <c r="E50">
-        <v>-18.97244696602925</v>
+        <v>-18.53275025378048</v>
       </c>
       <c r="F50">
-        <v>-0.8610193079631615</v>
+        <v>-0.518071889734555</v>
       </c>
       <c r="G50">
-        <v>-8.975931405469669</v>
+        <v>-7.921911166372364</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.045032413647937</v>
       </c>
       <c r="E51">
-        <v>-18.70880373777669</v>
+        <v>-17.42329223579728</v>
       </c>
       <c r="F51">
-        <v>-0.6335197979279165</v>
+        <v>-0.7704423026714523</v>
       </c>
       <c r="G51">
-        <v>-9.029750001487683</v>
+        <v>-6.365578562404343</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.291597175342034</v>
       </c>
       <c r="E52">
-        <v>-18.53098414891749</v>
+        <v>-17.7610077133933</v>
       </c>
       <c r="F52">
-        <v>-0.5086177325664042</v>
+        <v>-0.8708520290343916</v>
       </c>
       <c r="G52">
-        <v>-9.548855658299633</v>
+        <v>-5.927135175188221</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.55011485880239</v>
       </c>
       <c r="E53">
-        <v>-17.04608393638036</v>
+        <v>-16.90560161571441</v>
       </c>
       <c r="F53">
-        <v>-0.814569434218582</v>
+        <v>-0.3480146888790389</v>
       </c>
       <c r="G53">
-        <v>-9.0613186341111</v>
+        <v>-6.745084647969719</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.81694888702047</v>
       </c>
       <c r="E54">
-        <v>-17.16072678435854</v>
+        <v>-16.42483617269009</v>
       </c>
       <c r="F54">
-        <v>-0.6540318315560378</v>
+        <v>-1.070765247821607</v>
       </c>
       <c r="G54">
-        <v>-9.372460468485446</v>
+        <v>-6.440961346511026</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.094251208058643</v>
       </c>
       <c r="E55">
-        <v>-16.23600333504424</v>
+        <v>-15.50825944811558</v>
       </c>
       <c r="F55">
-        <v>-1.039625260415568</v>
+        <v>-0.7601075909541257</v>
       </c>
       <c r="G55">
-        <v>-9.599570218722411</v>
+        <v>-6.385196986108263</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.37157388207318</v>
       </c>
       <c r="E56">
-        <v>-15.33161273402438</v>
+        <v>-15.36042288566118</v>
       </c>
       <c r="F56">
-        <v>-0.7709451216849517</v>
+        <v>-0.4073846090050822</v>
       </c>
       <c r="G56">
-        <v>-9.795029305796973</v>
+        <v>-6.460218835843407</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.649379110290633</v>
       </c>
       <c r="E57">
-        <v>-14.85148127736113</v>
+        <v>-15.91772859636315</v>
       </c>
       <c r="F57">
-        <v>-0.9091665065160771</v>
+        <v>-0.9230308917367325</v>
       </c>
       <c r="G57">
-        <v>-10.1293037521654</v>
+        <v>-6.090631883052232</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.920397979149565</v>
       </c>
       <c r="E58">
-        <v>-14.62096383647468</v>
+        <v>-14.45753120953785</v>
       </c>
       <c r="F58">
-        <v>-0.9732407251226189</v>
+        <v>-1.039176285283251</v>
       </c>
       <c r="G58">
-        <v>-9.485570738082624</v>
+        <v>-7.495595174039949</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.176013305941555</v>
       </c>
       <c r="E59">
-        <v>-14.35009316370587</v>
+        <v>-14.32551260679224</v>
       </c>
       <c r="F59">
-        <v>-0.7975696783783306</v>
+        <v>-0.5688789760178599</v>
       </c>
       <c r="G59">
-        <v>-9.593581989376425</v>
+        <v>-6.976013740101878</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.414948244235251</v>
       </c>
       <c r="E60">
-        <v>-13.13511264439593</v>
+        <v>-13.42575916315623</v>
       </c>
       <c r="F60">
-        <v>-1.012506168382718</v>
+        <v>-1.463421337157407</v>
       </c>
       <c r="G60">
-        <v>-9.792611045507662</v>
+        <v>-6.96885411465917</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.623929388079065</v>
       </c>
       <c r="E61">
-        <v>-13.32541723609427</v>
+        <v>-12.83809456270684</v>
       </c>
       <c r="F61">
-        <v>-1.467027220461793</v>
+        <v>-1.427983779665644</v>
       </c>
       <c r="G61">
-        <v>-10.1861738842337</v>
+        <v>-6.694294619451074</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.802519378288624</v>
       </c>
       <c r="E62">
-        <v>-12.64598763835345</v>
+        <v>-12.1399351964703</v>
       </c>
       <c r="F62">
-        <v>-1.000730097384521</v>
+        <v>-1.090820851010786</v>
       </c>
       <c r="G62">
-        <v>-10.34894544213307</v>
+        <v>-7.890066911137953</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.943520381427565</v>
       </c>
       <c r="E63">
-        <v>-12.21418858477407</v>
+        <v>-11.10962584719315</v>
       </c>
       <c r="F63">
-        <v>-1.037393638632427</v>
+        <v>-1.06600793382733</v>
       </c>
       <c r="G63">
-        <v>-10.10508505583514</v>
+        <v>-8.603502914808017</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.0400601125797</v>
       </c>
       <c r="E64">
-        <v>-12.4017126934317</v>
+        <v>-11.96790752586691</v>
       </c>
       <c r="F64">
-        <v>-1.400179627790678</v>
+        <v>-0.7598160056283403</v>
       </c>
       <c r="G64">
-        <v>-10.3845827894902</v>
+        <v>-8.024304966356395</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.093987702588643</v>
       </c>
       <c r="E65">
-        <v>-11.76269519773532</v>
+        <v>-11.13682839055723</v>
       </c>
       <c r="F65">
-        <v>-1.644737707751774</v>
+        <v>-1.032951932618616</v>
       </c>
       <c r="G65">
-        <v>-9.989901054212396</v>
+        <v>-8.526226865861535</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.097222698358056</v>
       </c>
       <c r="E66">
-        <v>-12.20663509012927</v>
+        <v>-10.72998122876011</v>
       </c>
       <c r="F66">
-        <v>-1.158453735979755</v>
+        <v>-1.217181671368629</v>
       </c>
       <c r="G66">
-        <v>-10.45352125445414</v>
+        <v>-7.990665882928968</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.055798484062942</v>
       </c>
       <c r="E67">
-        <v>-11.79864222440821</v>
+        <v>-11.73737197108443</v>
       </c>
       <c r="F67">
-        <v>-1.457777670042134</v>
+        <v>-1.269349765294733</v>
       </c>
       <c r="G67">
-        <v>-10.71939207497282</v>
+        <v>-9.024490203327893</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.969429304768264</v>
       </c>
       <c r="E68">
-        <v>-11.3892636456408</v>
+        <v>-11.41375363307429</v>
       </c>
       <c r="F68">
-        <v>-1.423162681381351</v>
+        <v>-1.584915499023802</v>
       </c>
       <c r="G68">
-        <v>-10.61150879131984</v>
+        <v>-8.727470746545398</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.83934584462085</v>
       </c>
       <c r="E69">
-        <v>-11.22337205731782</v>
+        <v>-10.59219787860273</v>
       </c>
       <c r="F69">
-        <v>-1.895788531416011</v>
+        <v>-1.172226172418699</v>
       </c>
       <c r="G69">
-        <v>-9.701839332287184</v>
+        <v>-7.806087326545525</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.674325857159317</v>
       </c>
       <c r="E70">
-        <v>-12.14242132870051</v>
+        <v>-10.42804069582468</v>
       </c>
       <c r="F70">
-        <v>-1.605254403864738</v>
+        <v>-1.33323925797045</v>
       </c>
       <c r="G70">
-        <v>-9.975965706249434</v>
+        <v>-7.361613054103143</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.472507060787458</v>
       </c>
       <c r="E71">
-        <v>-11.42127995687503</v>
+        <v>-11.91532288568985</v>
       </c>
       <c r="F71">
-        <v>-2.271520246345214</v>
+        <v>-1.312621193314771</v>
       </c>
       <c r="G71">
-        <v>-9.426085472431451</v>
+        <v>-7.738221821031529</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.244445556186738</v>
       </c>
       <c r="E72">
-        <v>-11.4781123056713</v>
+        <v>-11.97853132588891</v>
       </c>
       <c r="F72">
-        <v>-2.045888704803282</v>
+        <v>-2.139656581330575</v>
       </c>
       <c r="G72">
-        <v>-9.337387491236541</v>
+        <v>-8.558920957479842</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.991863263271931</v>
       </c>
       <c r="E73">
-        <v>-12.34556414421059</v>
+        <v>-11.18910509450177</v>
       </c>
       <c r="F73">
-        <v>-2.499873803172745</v>
+        <v>-2.21879300442222</v>
       </c>
       <c r="G73">
-        <v>-9.574386843253674</v>
+        <v>-7.817843943393014</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.717048797848326</v>
       </c>
       <c r="E74">
-        <v>-11.78922752694626</v>
+        <v>-11.31063122297162</v>
       </c>
       <c r="F74">
-        <v>-2.023271789604647</v>
+        <v>-1.802962508625702</v>
       </c>
       <c r="G74">
-        <v>-8.627892234659368</v>
+        <v>-7.906430363054903</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.427855306930889</v>
       </c>
       <c r="E75">
-        <v>-11.81771162845451</v>
+        <v>-11.51116110897927</v>
       </c>
       <c r="F75">
-        <v>-2.456411850650064</v>
+        <v>-1.883360535271811</v>
       </c>
       <c r="G75">
-        <v>-8.532333219183661</v>
+        <v>-7.567844391557363</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.121563317475001</v>
       </c>
       <c r="E76">
-        <v>-12.6703417715667</v>
+        <v>-11.43963386202812</v>
       </c>
       <c r="F76">
-        <v>-2.419480746731054</v>
+        <v>-2.930517993233527</v>
       </c>
       <c r="G76">
-        <v>-8.295849018951362</v>
+        <v>-6.562894820881551</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.807178438999228</v>
       </c>
       <c r="E77">
-        <v>-12.78824512083041</v>
+        <v>-11.22619329662459</v>
       </c>
       <c r="F77">
-        <v>-2.406138232974162</v>
+        <v>-2.656585176801759</v>
       </c>
       <c r="G77">
-        <v>-8.387805253154799</v>
+        <v>-6.081241026949102</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.485469424557923</v>
       </c>
       <c r="E78">
-        <v>-12.67704844157206</v>
+        <v>-12.77059765762252</v>
       </c>
       <c r="F78">
-        <v>-2.418615102795128</v>
+        <v>-2.861721252063625</v>
       </c>
       <c r="G78">
-        <v>-7.955917746614448</v>
+        <v>-6.755266278468675</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.158380503325597</v>
       </c>
       <c r="E79">
-        <v>-13.29093290652586</v>
+        <v>-13.91780956340767</v>
       </c>
       <c r="F79">
-        <v>-2.83119177143345</v>
+        <v>-2.654364323794853</v>
       </c>
       <c r="G79">
-        <v>-7.379275869757634</v>
+        <v>-5.970033865856402</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.831681020338106</v>
       </c>
       <c r="E80">
-        <v>-14.03409624745064</v>
+        <v>-13.92476529948345</v>
       </c>
       <c r="F80">
-        <v>-2.520700616413931</v>
+        <v>-2.600647182825514</v>
       </c>
       <c r="G80">
-        <v>-7.385415035295355</v>
+        <v>-6.564243402942482</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.502071761960874</v>
       </c>
       <c r="E81">
-        <v>-14.06868020344722</v>
+        <v>-13.22961736846201</v>
       </c>
       <c r="F81">
-        <v>-2.918584532428798</v>
+        <v>-2.291488042589696</v>
       </c>
       <c r="G81">
-        <v>-6.739158761833361</v>
+        <v>-5.0385311585672</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.175378679375276</v>
       </c>
       <c r="E82">
-        <v>-14.40012827301662</v>
+        <v>-14.22043842439227</v>
       </c>
       <c r="F82">
-        <v>-3.178215585651233</v>
+        <v>-3.310542308044037</v>
       </c>
       <c r="G82">
-        <v>-6.841706779230687</v>
+        <v>-4.227370533192194</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.849787447483987</v>
       </c>
       <c r="E83">
-        <v>-14.54037511303418</v>
+        <v>-15.73100602760487</v>
       </c>
       <c r="F83">
-        <v>-3.031416456364118</v>
+        <v>-2.382087413801281</v>
       </c>
       <c r="G83">
-        <v>-6.66855015509567</v>
+        <v>-5.52999580496239</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.524544075875235</v>
       </c>
       <c r="E84">
-        <v>-15.69687039053506</v>
+        <v>-16.83425097924956</v>
       </c>
       <c r="F84">
-        <v>-3.013782171093322</v>
+        <v>-2.655461910603563</v>
       </c>
       <c r="G84">
-        <v>-5.882855090243515</v>
+        <v>-3.888384252664401</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.201985915300018</v>
       </c>
       <c r="E85">
-        <v>-16.54294330328414</v>
+        <v>-16.48437654894294</v>
       </c>
       <c r="F85">
-        <v>-2.655187720993236</v>
+        <v>-3.196973965487627</v>
       </c>
       <c r="G85">
-        <v>-6.084525529730105</v>
+        <v>-3.992910846662072</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.878169694828379</v>
       </c>
       <c r="E86">
-        <v>-17.0058393878742</v>
+        <v>-16.48554036676291</v>
       </c>
       <c r="F86">
-        <v>-3.412586403292699</v>
+        <v>-3.137781315985783</v>
       </c>
       <c r="G86">
-        <v>-5.720667589781722</v>
+        <v>-4.386887119304599</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.557156950010913</v>
       </c>
       <c r="E87">
-        <v>-18.57720628311379</v>
+        <v>-20.01131060270688</v>
       </c>
       <c r="F87">
-        <v>-3.434233300262656</v>
+        <v>-3.319800142137724</v>
       </c>
       <c r="G87">
-        <v>-6.105026602033516</v>
+        <v>-4.610213621083525</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.238867923435729</v>
       </c>
       <c r="E88">
-        <v>-19.68977989121427</v>
+        <v>-20.48561844179627</v>
       </c>
       <c r="F88">
-        <v>-3.453321370325365</v>
+        <v>-3.782520374769708</v>
       </c>
       <c r="G88">
-        <v>-5.785898274383483</v>
+        <v>-5.057191465575762</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.9262361139684487</v>
       </c>
       <c r="E89">
-        <v>-20.23996684077618</v>
+        <v>-21.24012561011025</v>
       </c>
       <c r="F89">
-        <v>-3.348194091603482</v>
+        <v>-3.177612534181995</v>
       </c>
       <c r="G89">
-        <v>-5.431306504118971</v>
+        <v>-3.750454823191583</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.6264942202865365</v>
       </c>
       <c r="E90">
-        <v>-22.87706480898091</v>
+        <v>-23.42900427798379</v>
       </c>
       <c r="F90">
-        <v>-3.913193675826525</v>
+        <v>-3.57543680774386</v>
       </c>
       <c r="G90">
-        <v>-5.821332186003926</v>
+        <v>-3.410182303812487</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.3444697403677258</v>
       </c>
       <c r="E91">
-        <v>-24.3201943772713</v>
+        <v>-22.96682822076096</v>
       </c>
       <c r="F91">
-        <v>-3.966373206351447</v>
+        <v>-3.702669070609447</v>
       </c>
       <c r="G91">
-        <v>-5.577435706268841</v>
+        <v>-2.813180447179318</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.09109472726844949</v>
       </c>
       <c r="E92">
-        <v>-24.85219950369241</v>
+        <v>-26.06971596844664</v>
       </c>
       <c r="F92">
-        <v>-4.142639020890946</v>
+        <v>-4.167147927237575</v>
       </c>
       <c r="G92">
-        <v>-5.554956057365085</v>
+        <v>-2.536537376280975</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.1259244199611565</v>
       </c>
       <c r="E93">
-        <v>-26.85755270545709</v>
+        <v>-28.27419975775062</v>
       </c>
       <c r="F93">
-        <v>-4.179932949732382</v>
+        <v>-4.14956417237835</v>
       </c>
       <c r="G93">
-        <v>-5.805703727716291</v>
+        <v>-2.460875688341739</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.3001743246911839</v>
       </c>
       <c r="E94">
-        <v>-27.90650578222381</v>
+        <v>-29.51623111654537</v>
       </c>
       <c r="F94">
-        <v>-4.333098910877414</v>
+        <v>-5.087133593154109</v>
       </c>
       <c r="G94">
-        <v>-6.757504071572217</v>
+        <v>-4.063365235986469</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.4256882366833471</v>
       </c>
       <c r="E95">
-        <v>-30.14150242939146</v>
+        <v>-30.63422304379604</v>
       </c>
       <c r="F95">
-        <v>-4.531379417513712</v>
+        <v>-4.660039785781725</v>
       </c>
       <c r="G95">
-        <v>-5.682109955236687</v>
+        <v>-4.7817230719957</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.4993243202841888</v>
       </c>
       <c r="E96">
-        <v>-32.30290458122346</v>
+        <v>-32.60122912766376</v>
       </c>
       <c r="F96">
-        <v>-4.474528562659581</v>
+        <v>-4.276023568457125</v>
       </c>
       <c r="G96">
-        <v>-6.434090468565548</v>
+        <v>-4.771771127005905</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.5225420086668199</v>
       </c>
       <c r="E97">
-        <v>-34.28518973639306</v>
+        <v>-34.93300379284934</v>
       </c>
       <c r="F97">
-        <v>-4.574653330635958</v>
+        <v>-4.753797721900185</v>
       </c>
       <c r="G97">
-        <v>-6.877534437438264</v>
+        <v>-4.808944086052853</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.4929958325600844</v>
       </c>
       <c r="E98">
-        <v>-36.72792560018858</v>
+        <v>-35.8834467102902</v>
       </c>
       <c r="F98">
-        <v>-4.802220766798232</v>
+        <v>-5.089814190069568</v>
       </c>
       <c r="G98">
-        <v>-7.416078050768366</v>
+        <v>-5.987512933103563</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.423751021487613</v>
       </c>
       <c r="E99">
-        <v>-38.3705095419098</v>
+        <v>-38.51872876041786</v>
       </c>
       <c r="F99">
-        <v>-4.804974260045138</v>
+        <v>-5.349939778631474</v>
       </c>
       <c r="G99">
-        <v>-7.409843729805421</v>
+        <v>-5.590360437991494</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>0.3083159822005524</v>
       </c>
       <c r="E100">
-        <v>-40.19807938260735</v>
+        <v>-40.58128564584743</v>
       </c>
       <c r="F100">
-        <v>-5.010641318812199</v>
+        <v>-5.228632827798112</v>
       </c>
       <c r="G100">
-        <v>-7.960327708390342</v>
+        <v>-5.592696667741818</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>0.1743297483988271</v>
       </c>
       <c r="E101">
-        <v>-42.82899145531761</v>
+        <v>-42.4130579104241</v>
       </c>
       <c r="F101">
-        <v>-5.184518950129426</v>
+        <v>-5.547084593558534</v>
       </c>
       <c r="G101">
-        <v>-7.98179017861067</v>
+        <v>-6.147757950402164</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.005266162408711215</v>
       </c>
       <c r="E102">
-        <v>-44.42398113521821</v>
+        <v>-44.77379216688873</v>
       </c>
       <c r="F102">
-        <v>-5.059563040886733</v>
+        <v>-5.289560078641418</v>
       </c>
       <c r="G102">
-        <v>-8.244766961713927</v>
+        <v>-6.335509448033592</v>
       </c>
     </row>
   </sheetData>
